--- a/data/baidu/china_erotic.xlsx
+++ b/data/baidu/china_erotic.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>色，戒</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>色，戒</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -660,16 +668,24 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>爱神</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>爱神</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -737,16 +753,24 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>色情男女</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>色情男女</t>
+        </is>
+      </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
@@ -814,16 +838,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>唐朝豪放女</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>唐朝豪放女</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -891,16 +923,24 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时</t>
+        </is>
+      </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
@@ -968,16 +1008,24 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>性工作者十日谈</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>性工作者十日谈</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
@@ -1045,16 +1093,24 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>风月奇谭</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>风月奇谭</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -1122,16 +1178,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>大鸿米店</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>大鸿米店</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1199,16 +1263,24 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>灭门惨案2：借种</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>灭门惨案2</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1276,16 +1348,24 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>天边一朵云</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>天边一朵云</t>
+        </is>
+      </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
@@ -1350,24 +1430,30 @@
           <t>https://movie.douban.com/subject/4883425/</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>4771.571428571428</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>花</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>花</t>
+        </is>
+      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1430,16 +1516,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>惊变</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>惊变</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1507,16 +1601,24 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>爱奴</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>爱奴</t>
+        </is>
+      </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
@@ -1584,16 +1686,24 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>玉蒲团之偷情宝鉴</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>玉蒲团之偷情宝鉴</t>
+        </is>
+      </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
@@ -1661,16 +1771,24 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>北地胭脂</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>北地胭脂</t>
+        </is>
+      </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
@@ -1738,16 +1856,24 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>慈禧秘密生活</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>慈禧秘密生活</t>
+        </is>
+      </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
@@ -1815,16 +1941,24 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>玉蒲团之玉女心经</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>玉蒲团之玉女心经</t>
+        </is>
+      </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
@@ -1892,16 +2026,24 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>台北晚九朝五</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>台北晚九朝五</t>
+        </is>
+      </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
@@ -1969,16 +2111,24 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>打蛇</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>打蛇</t>
+        </is>
+      </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
@@ -2046,16 +2196,24 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>风花雪月</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>风花雪月</t>
+        </is>
+      </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
@@ -2123,16 +2281,24 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>挡不住的疯情</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>挡不住的疯情</t>
+        </is>
+      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -2200,16 +2366,24 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>香港奇案之强奸</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>香港奇案之强奸</t>
+        </is>
+      </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
@@ -2277,16 +2451,24 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>三十年细说从头</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>三十年细说从头</t>
+        </is>
+      </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -2351,24 +2533,30 @@
           <t>https://movie.douban.com/subject/20515071/</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>5866.714285714285</v>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>飞虎出征</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>飞虎出征</t>
+        </is>
+      </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2431,16 +2619,24 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>种鬼</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>种鬼</t>
+        </is>
+      </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
@@ -2508,16 +2704,24 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>子曰：食色性也</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>子曰</t>
+        </is>
+      </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
@@ -2585,16 +2789,24 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>诱僧</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>诱僧</t>
+        </is>
+      </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
@@ -2662,16 +2874,24 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>满清十大酷刑</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>满清十大酷刑</t>
+        </is>
+      </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
@@ -2739,16 +2959,24 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>赤裸羔羊</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>赤裸羔羊</t>
+        </is>
+      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -2816,16 +3044,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>蛇杀手</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>蛇杀手</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2893,16 +3129,24 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>灭门惨案之孽杀</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>灭门惨案之孽杀</t>
+        </is>
+      </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
@@ -2970,16 +3214,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>正牌韦小宝之奉旨沟女</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>正牌韦小宝之奉旨沟女</t>
+        </is>
+      </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
@@ -3047,16 +3299,24 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>南洋十大邪术</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>南洋十大邪术</t>
+        </is>
+      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
@@ -3124,16 +3384,24 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时1997</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时1997</t>
+        </is>
+      </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
@@ -3201,16 +3469,24 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>聊斋艳谭之灯草和尚</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>聊斋艳谭之灯草和尚</t>
+        </is>
+      </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
@@ -3278,16 +3554,24 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>不扣钮的女孩</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>不扣钮的女孩</t>
+        </is>
+      </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -3355,16 +3639,24 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>聊斋艳谭</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>聊斋艳谭</t>
+        </is>
+      </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
@@ -3432,16 +3724,24 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>金瓶双艳</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>金瓶双艳</t>
+        </is>
+      </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
@@ -3509,16 +3809,24 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>一乐也</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>一乐也</t>
+        </is>
+      </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
@@ -3586,16 +3894,24 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>卿本佳人</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>卿本佳人</t>
+        </is>
+      </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
@@ -3663,16 +3979,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>女机械人</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>女机械人</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3740,16 +4064,24 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>牛鬼蛇神</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>牛鬼蛇神</t>
+        </is>
+      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
@@ -3817,16 +4149,24 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>剑奴</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>剑奴</t>
+        </is>
+      </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
@@ -3894,16 +4234,24 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>捉奸趣事</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>捉奸趣事</t>
+        </is>
+      </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
@@ -3971,16 +4319,24 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>金瓶风月</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>金瓶风月</t>
+        </is>
+      </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
@@ -4048,16 +4404,24 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>少女潘金莲</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>少女潘金莲</t>
+        </is>
+      </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
@@ -4125,16 +4489,24 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>红灯区</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>红灯区</t>
+        </is>
+      </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
@@ -4202,16 +4574,24 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>玉蒲团之官人我要</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>玉蒲团之官人我要</t>
+        </is>
+      </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
@@ -4279,16 +4659,24 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>赤裸天使</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>赤裸天使</t>
+        </is>
+      </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
@@ -4356,16 +4744,24 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>足本玉蒲团</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>足本玉蒲团</t>
+        </is>
+      </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
@@ -4433,16 +4829,24 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>敦煌夜谭</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>敦煌夜谭</t>
+        </is>
+      </c>
       <c r="T52" t="n">
         <v>0</v>
       </c>
@@ -4510,16 +4914,24 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>囡囡</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>囡囡</t>
+        </is>
+      </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -4587,16 +4999,24 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>晚9朝5</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>晚9朝5</t>
+        </is>
+      </c>
       <c r="T54" t="n">
         <v>0</v>
       </c>
@@ -4664,16 +5084,24 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>暴劫倾情</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>暴劫倾情</t>
+        </is>
+      </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
@@ -4741,16 +5169,24 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>血恋</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>血恋</t>
+        </is>
+      </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
@@ -4818,16 +5254,24 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>军阀趣史</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>军阀趣史</t>
+        </is>
+      </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
@@ -4895,16 +5339,24 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>金瓶梅</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>金瓶梅</t>
+        </is>
+      </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
@@ -4972,16 +5424,24 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>骗财骗色</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>骗财骗色</t>
+        </is>
+      </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
@@ -5049,16 +5509,24 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>人肉叉烧包2之天诛地灭</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>人肉叉烧包2之天诛地灭</t>
+        </is>
+      </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
@@ -5126,16 +5594,24 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>金瓶梅2：爱的奴隶</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>金瓶梅2</t>
+        </is>
+      </c>
       <c r="T61" t="n">
         <v>0</v>
       </c>
@@ -5203,16 +5679,24 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>我为卿狂</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>我为卿狂</t>
+        </is>
+      </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -5280,16 +5764,24 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>大内密探之零零性性</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>大内密探之零零性性</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -5357,16 +5849,24 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>帮帮我，爱神</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>帮帮我，爱神</t>
+        </is>
+      </c>
       <c r="T64" t="n">
         <v>0</v>
       </c>
@@ -5434,16 +5934,24 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>爱的精灵</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>爱的精灵</t>
+        </is>
+      </c>
       <c r="T65" t="n">
         <v>0</v>
       </c>
@@ -5511,16 +6019,24 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>舞男情未了</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>舞男情未了</t>
+        </is>
+      </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
@@ -5588,16 +6104,24 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>偷窥无罪</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>偷窥无罪</t>
+        </is>
+      </c>
       <c r="T67" t="n">
         <v>0</v>
       </c>
@@ -5665,16 +6189,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>满清禁宫奇案</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>满清禁宫奇案</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5742,16 +6274,24 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>情欲电影院</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>情欲电影院</t>
+        </is>
+      </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
@@ -5819,16 +6359,24 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>她来自胡志明市</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>她来自胡志明市</t>
+        </is>
+      </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
@@ -5896,16 +6444,24 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>三分之一情人</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>三分之一情人</t>
+        </is>
+      </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
@@ -5973,16 +6529,24 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>西厢艳谭</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>西厢艳谭</t>
+        </is>
+      </c>
       <c r="T72" t="n">
         <v>0</v>
       </c>
@@ -6050,16 +6614,24 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>猎艳</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>猎艳</t>
+        </is>
+      </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -6124,24 +6696,30 @@
           <t>https://movie.douban.com/subject/30334399/</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>330</v>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>三夫</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>三夫</t>
+        </is>
+      </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -6204,16 +6782,24 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>女欢</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>女欢</t>
+        </is>
+      </c>
       <c r="T75" t="n">
         <v>0</v>
       </c>
@@ -6281,16 +6867,24 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>强奸2：制服诱惑</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>强奸2</t>
+        </is>
+      </c>
       <c r="T76" t="n">
         <v>0</v>
       </c>
@@ -6358,16 +6952,24 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>港澳传奇</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>港澳传奇</t>
+        </is>
+      </c>
       <c r="T77" t="n">
         <v>0</v>
       </c>
@@ -6435,16 +7037,24 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>赤裸狂奔</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>赤裸狂奔</t>
+        </is>
+      </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
@@ -6509,24 +7119,30 @@
           <t>https://movie.douban.com/subject/6383557/</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>5985</v>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>喜爱夜蒲</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>喜爱夜蒲</t>
+        </is>
+      </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -6589,16 +7205,24 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>兽性新人类</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>兽性新人类</t>
+        </is>
+      </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
@@ -6666,16 +7290,24 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>我来自北京</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>我来自北京</t>
+        </is>
+      </c>
       <c r="T81" t="n">
         <v>0</v>
       </c>
@@ -6743,16 +7375,24 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>鸡鸭恋</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>鸡鸭恋</t>
+        </is>
+      </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
@@ -6820,16 +7460,24 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>整容</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>整容</t>
+        </is>
+      </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
@@ -6897,16 +7545,24 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>伟哥的故事</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>伟哥的故事</t>
+        </is>
+      </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -6974,16 +7630,24 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>落山风</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>落山风</t>
+        </is>
+      </c>
       <c r="T85" t="n">
         <v>0</v>
       </c>
@@ -7051,16 +7715,24 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>拈花惹草</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>拈花惹草</t>
+        </is>
+      </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
@@ -7128,16 +7800,24 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>不文小丈夫</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>不文小丈夫</t>
+        </is>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7205,16 +7885,24 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>聊斋花弄月</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>聊斋花弄月</t>
+        </is>
+      </c>
       <c r="T88" t="n">
         <v>0</v>
       </c>
@@ -7282,16 +7970,24 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>亲密杀机</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>亲密杀机</t>
+        </is>
+      </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
@@ -7359,16 +8055,24 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>三级七日情</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>三级七日情</t>
+        </is>
+      </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
@@ -7436,16 +8140,24 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3486421599, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>亚洲铜</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>亚洲铜</t>
+        </is>
+      </c>
       <c r="T91" t="n">
         <v>0</v>
       </c>
@@ -7513,16 +8225,24 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3486644274, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>3D肉蒲团之极乐宝鉴</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>3D肉蒲团之极乐宝鉴</t>
+        </is>
+      </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
@@ -7590,16 +8310,24 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>香港舞男</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>香港舞男</t>
+        </is>
+      </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -7667,16 +8395,24 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>人骨麻将</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>人骨麻将</t>
+        </is>
+      </c>
       <c r="T94" t="n">
         <v>0</v>
       </c>
@@ -7744,16 +8480,24 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>桃色</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>桃色</t>
+        </is>
+      </c>
       <c r="T95" t="n">
         <v>0</v>
       </c>
@@ -7821,16 +8565,24 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>杏林春暖</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>杏林春暖</t>
+        </is>
+      </c>
       <c r="T96" t="n">
         <v>0</v>
       </c>
@@ -7898,16 +8650,24 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>哎呀女朋友</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>哎呀女朋友</t>
+        </is>
+      </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
@@ -7975,16 +8735,24 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>OL诱惑</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>OL诱惑</t>
+        </is>
+      </c>
       <c r="T98" t="n">
         <v>0</v>
       </c>
@@ -8052,16 +8820,24 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>南洋第一邪降</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>南洋第一邪降</t>
+        </is>
+      </c>
       <c r="T99" t="n">
         <v>0</v>
       </c>
@@ -8129,16 +8905,24 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>特区爱奴</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>特区爱奴</t>
+        </is>
+      </c>
       <c r="T100" t="n">
         <v>0</v>
       </c>
@@ -8206,16 +8990,24 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>赶尸艳谈</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>赶尸艳谈</t>
+        </is>
+      </c>
       <c r="T101" t="n">
         <v>0</v>
       </c>
@@ -8283,16 +9075,24 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>半妖乳娘</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>半妖乳娘</t>
+        </is>
+      </c>
       <c r="T102" t="n">
         <v>0</v>
       </c>
@@ -8360,16 +9160,24 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>禁色</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>禁色</t>
+        </is>
+      </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
@@ -8434,24 +9242,30 @@
           <t>https://movie.douban.com/subject/25981796/</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>64.57142857142857</v>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>情欲房</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>情欲房</t>
+        </is>
+      </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -8514,16 +9328,24 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>满清十大酷刑之赤裸凌迟</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>满清十大酷刑之赤裸凌迟</t>
+        </is>
+      </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -8591,16 +9413,24 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>竹夫人</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>竹夫人</t>
+        </is>
+      </c>
       <c r="T106" t="n">
         <v>0</v>
       </c>
@@ -8668,16 +9498,24 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>吸我一个吻</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>吸我一个吻</t>
+        </is>
+      </c>
       <c r="T107" t="n">
         <v>0</v>
       </c>
@@ -8745,16 +9583,24 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>女集中营</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>女集中营</t>
+        </is>
+      </c>
       <c r="T108" t="n">
         <v>0</v>
       </c>
@@ -8822,16 +9668,24 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>不文女学堂</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>不文女学堂</t>
+        </is>
+      </c>
       <c r="T109" t="n">
         <v>0</v>
       </c>
@@ -8899,16 +9753,24 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>心锁</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>心锁</t>
+        </is>
+      </c>
       <c r="T110" t="n">
         <v>0</v>
       </c>
@@ -8976,16 +9838,24 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>瞓上你的床</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>瞓上你的床</t>
+        </is>
+      </c>
       <c r="T111" t="n">
         <v>0</v>
       </c>
@@ -9053,16 +9923,24 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>聊斋艳谭续集五通神</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>聊斋艳谭续集五通神</t>
+        </is>
+      </c>
       <c r="T112" t="n">
         <v>0</v>
       </c>
@@ -9130,16 +10008,24 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>同居关系</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>同居关系</t>
+        </is>
+      </c>
       <c r="T113" t="n">
         <v>0</v>
       </c>
@@ -9207,16 +10093,24 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>皇帝保重</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>皇帝保重</t>
+        </is>
+      </c>
       <c r="T114" t="n">
         <v>0</v>
       </c>
@@ -9284,16 +10178,24 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>周末狂热</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>周末狂热</t>
+        </is>
+      </c>
       <c r="T115" t="n">
         <v>0</v>
       </c>
@@ -9361,16 +10263,24 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>应召名册</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>应召名册</t>
+        </is>
+      </c>
       <c r="T116" t="n">
         <v>0</v>
       </c>
@@ -9438,16 +10348,24 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>偶遇</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>偶遇</t>
+        </is>
+      </c>
       <c r="T117" t="n">
         <v>0</v>
       </c>
@@ -9515,16 +10433,24 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>情劫</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>情劫</t>
+        </is>
+      </c>
       <c r="T118" t="n">
         <v>0</v>
       </c>
@@ -9592,16 +10518,24 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>何日金再来</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>何日金再来</t>
+        </is>
+      </c>
       <c r="T119" t="n">
         <v>0</v>
       </c>
@@ -9666,24 +10600,30 @@
           <t>https://movie.douban.com/subject/26279166/</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
+      <c r="O120" t="n">
+        <v>2102</v>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>鸭王</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>鸭王</t>
+        </is>
+      </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -9746,16 +10686,24 @@
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>玉女聊斋</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>玉女聊斋</t>
+        </is>
+      </c>
       <c r="T121" t="n">
         <v>0</v>
       </c>
@@ -9820,24 +10768,30 @@
           <t>https://movie.douban.com/subject/4275580/</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
+      <c r="O122" t="n">
+        <v>488</v>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>花为眉</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>花为眉</t>
+        </is>
+      </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -9897,21 +10851,27 @@
           <t>https://movie.douban.com/subject/26752558/</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>非分熟女</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>非分熟女</t>
+        </is>
+      </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -9977,16 +10937,24 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>偷情男女</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>偷情男女</t>
+        </is>
+      </c>
       <c r="T124" t="n">
         <v>0</v>
       </c>
@@ -10054,16 +11022,24 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>那个少女不多情之脱的疑惑</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>那个少女不多情之脱的疑惑</t>
+        </is>
+      </c>
       <c r="T125" t="n">
         <v>0</v>
       </c>
@@ -10131,16 +11107,24 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>现代豪放女</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>现代豪放女</t>
+        </is>
+      </c>
       <c r="T126" t="n">
         <v>0</v>
       </c>
@@ -10208,16 +11192,24 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>太太的情人</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>太太的情人</t>
+        </is>
+      </c>
       <c r="T127" t="n">
         <v>0</v>
       </c>
@@ -10285,16 +11277,24 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>野浪花</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>野浪花</t>
+        </is>
+      </c>
       <c r="T128" t="n">
         <v>0</v>
       </c>
@@ -10362,16 +11362,24 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>狐仙</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>狐仙</t>
+        </is>
+      </c>
       <c r="T129" t="n">
         <v>0</v>
       </c>
@@ -10436,24 +11444,30 @@
           <t>https://movie.douban.com/subject/10744833/</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="n">
+        <v>74631.14285714286</v>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>喜爱夜蒲2</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>喜爱夜蒲2</t>
+        </is>
+      </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -10516,16 +11530,24 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>性爱交叉点</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>性爱交叉点</t>
+        </is>
+      </c>
       <c r="T131" t="n">
         <v>0</v>
       </c>
@@ -10593,16 +11615,24 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>素女经之挑情宝鉴</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>素女经之挑情宝鉴</t>
+        </is>
+      </c>
       <c r="T132" t="n">
         <v>0</v>
       </c>
@@ -10670,16 +11700,24 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>发电俏娇娃</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>发电俏娇娃</t>
+        </is>
+      </c>
       <c r="T133" t="n">
         <v>0</v>
       </c>
@@ -10747,16 +11785,24 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>二奶村之杀夫</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>二奶村之杀夫</t>
+        </is>
+      </c>
       <c r="T134" t="n">
         <v>0</v>
       </c>
@@ -10824,16 +11870,24 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>屠夫</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>屠夫</t>
+        </is>
+      </c>
       <c r="T135" t="n">
         <v>0</v>
       </c>
@@ -10901,16 +11955,24 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>情难自制</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>情难自制</t>
+        </is>
+      </c>
       <c r="T136" t="n">
         <v>0</v>
       </c>
@@ -10978,16 +12040,24 @@
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>性 丈夫 情人</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>性 丈夫 情人</t>
+        </is>
+      </c>
       <c r="T137" t="n">
         <v>0</v>
       </c>
@@ -11055,16 +12125,24 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>金瓶艳史</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>金瓶艳史</t>
+        </is>
+      </c>
       <c r="T138" t="n">
         <v>0</v>
       </c>
@@ -11132,16 +12210,24 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>灵幻新娘</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>灵幻新娘</t>
+        </is>
+      </c>
       <c r="T139" t="n">
         <v>0</v>
       </c>
@@ -11209,16 +12295,24 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时3之蜜桃仙子</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时3之蜜桃仙子</t>
+        </is>
+      </c>
       <c r="T140" t="n">
         <v>0</v>
       </c>
@@ -11286,16 +12380,24 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>狂情</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>狂情</t>
+        </is>
+      </c>
       <c r="T141" t="n">
         <v>0</v>
       </c>
@@ -11363,16 +12465,24 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>田螺艳鬼</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>田螺艳鬼</t>
+        </is>
+      </c>
       <c r="T142" t="n">
         <v>0</v>
       </c>
@@ -11440,16 +12550,24 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>新报仇</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>新报仇</t>
+        </is>
+      </c>
       <c r="T143" t="n">
         <v>0</v>
       </c>
@@ -11517,16 +12635,24 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>欲海双艳</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>欲海双艳</t>
+        </is>
+      </c>
       <c r="T144" t="n">
         <v>0</v>
       </c>
@@ -11591,24 +12717,30 @@
           <t>https://movie.douban.com/subject/24858573/</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="n">
+        <v>13132</v>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>3D豪情</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>3D豪情</t>
+        </is>
+      </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -11671,16 +12803,24 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>香港奇案之雾夜屠夫</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>香港奇案之雾夜屠夫</t>
+        </is>
+      </c>
       <c r="T146" t="n">
         <v>0</v>
       </c>
@@ -11748,16 +12888,24 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>五月樱唇</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>五月樱唇</t>
+        </is>
+      </c>
       <c r="T147" t="n">
         <v>0</v>
       </c>
@@ -11825,16 +12973,24 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>三级蔷薇之恋</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>三级蔷薇之恋</t>
+        </is>
+      </c>
       <c r="T148" t="n">
         <v>0</v>
       </c>
@@ -11902,16 +13058,24 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>好色妖姬杨贵妃</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>好色妖姬杨贵妃</t>
+        </is>
+      </c>
       <c r="T149" t="n">
         <v>0</v>
       </c>
@@ -11979,16 +13143,24 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>红楼春梦</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>红楼春梦</t>
+        </is>
+      </c>
       <c r="T150" t="n">
         <v>0</v>
       </c>
@@ -12056,16 +13228,24 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>艳客临门</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>艳客临门</t>
+        </is>
+      </c>
       <c r="T151" t="n">
         <v>0</v>
       </c>
@@ -12133,16 +13313,24 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>虾碌情圣</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>虾碌情圣</t>
+        </is>
+      </c>
       <c r="T152" t="n">
         <v>0</v>
       </c>
@@ -12210,16 +13398,24 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>奸魔</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>奸魔</t>
+        </is>
+      </c>
       <c r="T153" t="n">
         <v>0</v>
       </c>
@@ -12287,16 +13483,24 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>山庄情挑</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>山庄情挑</t>
+        </is>
+      </c>
       <c r="T154" t="n">
         <v>0</v>
       </c>
@@ -12364,16 +13568,24 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>红粉幽魂</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>红粉幽魂</t>
+        </is>
+      </c>
       <c r="T155" t="n">
         <v>0</v>
       </c>
@@ -12441,16 +13653,24 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>桃色经纪</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>桃色经纪</t>
+        </is>
+      </c>
       <c r="T156" t="n">
         <v>0</v>
       </c>
@@ -12518,16 +13738,24 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>97风流梦</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>97风流梦</t>
+        </is>
+      </c>
       <c r="T157" t="n">
         <v>0</v>
       </c>
@@ -12595,16 +13823,24 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>一代女皇艳史</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>一代女皇艳史</t>
+        </is>
+      </c>
       <c r="T158" t="n">
         <v>0</v>
       </c>
@@ -12669,24 +13905,30 @@
           <t>https://movie.douban.com/subject/26614645/</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="n">
+        <v>3441.285714285714</v>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>鸭王2</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>鸭王2</t>
+        </is>
+      </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -12749,16 +13991,24 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>怨妇.狂娃.疯杀手</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>怨妇.狂娃.疯杀手</t>
+        </is>
+      </c>
       <c r="T160" t="n">
         <v>0</v>
       </c>
@@ -12826,16 +14076,24 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>唐朝禁宫秘史</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>唐朝禁宫秘史</t>
+        </is>
+      </c>
       <c r="T161" t="n">
         <v>0</v>
       </c>
@@ -12903,16 +14161,24 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>双姝艳</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>双姝艳</t>
+        </is>
+      </c>
       <c r="T162" t="n">
         <v>0</v>
       </c>
@@ -12980,16 +14246,24 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>赤裸迷情</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>赤裸迷情</t>
+        </is>
+      </c>
       <c r="T163" t="n">
         <v>0</v>
       </c>
@@ -13057,16 +14331,24 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>引郎入室</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>引郎入室</t>
+        </is>
+      </c>
       <c r="T164" t="n">
         <v>0</v>
       </c>
@@ -13134,16 +14416,24 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>鸭之一族</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>鸭之一族</t>
+        </is>
+      </c>
       <c r="T165" t="n">
         <v>0</v>
       </c>
@@ -13208,21 +14498,27 @@
           <t>https://movie.douban.com/subject/37105408/</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr"/>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>坏鸟</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>坏鸟</t>
+        </is>
+      </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -13288,16 +14584,24 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>三剑侠与飞机妹</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>三剑侠与飞机妹</t>
+        </is>
+      </c>
       <c r="T167" t="n">
         <v>0</v>
       </c>
@@ -13365,16 +14669,24 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>猛鬼咒</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>猛鬼咒</t>
+        </is>
+      </c>
       <c r="T168" t="n">
         <v>0</v>
       </c>
@@ -13442,16 +14754,24 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>烈火女警花</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>烈火女警花</t>
+        </is>
+      </c>
       <c r="T169" t="n">
         <v>0</v>
       </c>
@@ -13519,16 +14839,24 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>情不自禁II霎时冲动</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>情不自禁II霎时冲动</t>
+        </is>
+      </c>
       <c r="T170" t="n">
         <v>0</v>
       </c>
@@ -13596,16 +14924,24 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>兽性诱惑之赤裸性游戏</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>兽性诱惑之赤裸性游戏</t>
+        </is>
+      </c>
       <c r="T171" t="n">
         <v>0</v>
       </c>
@@ -13673,16 +15009,24 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>93夜之女</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>93夜之女</t>
+        </is>
+      </c>
       <c r="T172" t="n">
         <v>0</v>
       </c>
@@ -13750,16 +15094,24 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>师生畸恋</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>师生畸恋</t>
+        </is>
+      </c>
       <c r="T173" t="n">
         <v>0</v>
       </c>
@@ -13827,16 +15179,24 @@
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>妲己传</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>妲己传</t>
+        </is>
+      </c>
       <c r="T174" t="n">
         <v>0</v>
       </c>
@@ -13901,24 +15261,30 @@
           <t>https://movie.douban.com/subject/22734960/</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr"/>
+      <c r="O175" t="n">
+        <v>573.7142857142857</v>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>微交少女</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>微交少女</t>
+        </is>
+      </c>
       <c r="T175" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U175" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -13981,16 +15347,24 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>人皮高跟鞋</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>人皮高跟鞋</t>
+        </is>
+      </c>
       <c r="T176" t="n">
         <v>0</v>
       </c>
@@ -14055,24 +15429,30 @@
           <t>https://movie.douban.com/subject/6796160/</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr"/>
+      <c r="O177" t="n">
+        <v>14822.28571428571</v>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时33D</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时33D</t>
+        </is>
+      </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -14135,16 +15515,24 @@
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>世外情缘</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>世外情缘</t>
+        </is>
+      </c>
       <c r="T178" t="n">
         <v>0</v>
       </c>
@@ -14212,16 +15600,24 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3490156182, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>喜爱夜蒲3</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>喜爱夜蒲3</t>
+        </is>
+      </c>
       <c r="T179" t="n">
         <v>0</v>
       </c>
@@ -14289,16 +15685,24 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>青春梦里人</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>青春梦里人</t>
+        </is>
+      </c>
       <c r="T180" t="n">
         <v>0</v>
       </c>
@@ -14366,16 +15770,24 @@
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>兼职女郎</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>兼职女郎</t>
+        </is>
+      </c>
       <c r="T181" t="n">
         <v>0</v>
       </c>
@@ -14443,16 +15855,24 @@
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>兽性新人类2：失忆性行为</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>兽性新人类2</t>
+        </is>
+      </c>
       <c r="T182" t="n">
         <v>0</v>
       </c>
@@ -14520,16 +15940,24 @@
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>三度诱惑</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>三度诱惑</t>
+        </is>
+      </c>
       <c r="T183" t="n">
         <v>0</v>
       </c>
@@ -14597,16 +16025,24 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>赌城快活女</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>赌城快活女</t>
+        </is>
+      </c>
       <c r="T184" t="n">
         <v>0</v>
       </c>
@@ -14671,24 +16107,30 @@
           <t>https://movie.douban.com/subject/24294773/</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr"/>
+      <c r="O185" t="n">
+        <v>1391.571428571429</v>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>游</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>游</t>
+        </is>
+      </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U185" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -14751,16 +16193,24 @@
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>不羁的心</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>不羁的心</t>
+        </is>
+      </c>
       <c r="T186" t="n">
         <v>0</v>
       </c>
@@ -14828,16 +16278,24 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>亲蜜情人之无限诱惑</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>亲蜜情人之无限诱惑</t>
+        </is>
+      </c>
       <c r="T187" t="n">
         <v>0</v>
       </c>
@@ -14905,16 +16363,24 @@
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>玉女性重伤</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>玉女性重伤</t>
+        </is>
+      </c>
       <c r="T188" t="n">
         <v>0</v>
       </c>
@@ -14979,24 +16445,30 @@
           <t>https://movie.douban.com/subject/25853739/</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr"/>
+      <c r="O189" t="n">
+        <v>378.5714285714286</v>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>花街柳巷</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>花街柳巷</t>
+        </is>
+      </c>
       <c r="T189" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U189" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -15059,16 +16531,24 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>淫妖豪情</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>淫妖豪情</t>
+        </is>
+      </c>
       <c r="T190" t="n">
         <v>0</v>
       </c>
@@ -15133,24 +16613,30 @@
           <t>https://movie.douban.com/subject/5989846/</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr"/>
+      <c r="O191" t="n">
+        <v>1735.571428571429</v>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>爱很烂</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>爱很烂</t>
+        </is>
+      </c>
       <c r="T191" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U191" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -15213,16 +16699,24 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>鬼叫春</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>鬼叫春</t>
+        </is>
+      </c>
       <c r="T192" t="n">
         <v>0</v>
       </c>
@@ -15290,16 +16784,24 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>新应召女郎</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>新应召女郎</t>
+        </is>
+      </c>
       <c r="T193" t="n">
         <v>0</v>
       </c>
@@ -15367,16 +16869,24 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>山中艳谭</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>山中艳谭</t>
+        </is>
+      </c>
       <c r="T194" t="n">
         <v>0</v>
       </c>
@@ -15444,16 +16954,24 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>烹夫</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>烹夫</t>
+        </is>
+      </c>
       <c r="T195" t="n">
         <v>0</v>
       </c>
@@ -15521,16 +17039,24 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>禁室培欲之爱的俘虏</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>禁室培欲之爱的俘虏</t>
+        </is>
+      </c>
       <c r="T196" t="n">
         <v>0</v>
       </c>
@@ -15598,16 +17124,24 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>属鸡的女人</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>属鸡的女人</t>
+        </is>
+      </c>
       <c r="T197" t="n">
         <v>0</v>
       </c>
@@ -15675,16 +17209,24 @@
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>终极强奸2：原始兽性</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>终极强奸2</t>
+        </is>
+      </c>
       <c r="T198" t="n">
         <v>0</v>
       </c>
@@ -15752,16 +17294,24 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>处女降</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>处女降</t>
+        </is>
+      </c>
       <c r="T199" t="n">
         <v>0</v>
       </c>
@@ -15829,16 +17379,24 @@
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>撞够本</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>撞够本</t>
+        </is>
+      </c>
       <c r="T200" t="n">
         <v>0</v>
       </c>
@@ -15906,16 +17464,24 @@
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>性爱韦小宝之玩女大王</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>性爱韦小宝之玩女大王</t>
+        </is>
+      </c>
       <c r="T201" t="n">
         <v>0</v>
       </c>
@@ -15983,16 +17549,24 @@
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>大波诱惑</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>大波诱惑</t>
+        </is>
+      </c>
       <c r="T202" t="n">
         <v>0</v>
       </c>
@@ -16056,16 +17630,24 @@
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时2005之三人同眠</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时2005之三人同眠</t>
+        </is>
+      </c>
       <c r="T203" t="n">
         <v>0</v>
       </c>
@@ -16133,16 +17715,24 @@
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>强奸案中案</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>强奸案中案</t>
+        </is>
+      </c>
       <c r="T204" t="n">
         <v>0</v>
       </c>
@@ -16210,16 +17800,24 @@
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>省港流莺</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>省港流莺</t>
+        </is>
+      </c>
       <c r="T205" t="n">
         <v>0</v>
       </c>
@@ -16287,16 +17885,24 @@
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>羔羊大律师</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>羔羊大律师</t>
+        </is>
+      </c>
       <c r="T206" t="n">
         <v>0</v>
       </c>
@@ -16364,16 +17970,24 @@
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>我爱狐狸精</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>我爱狐狸精</t>
+        </is>
+      </c>
       <c r="T207" t="n">
         <v>0</v>
       </c>
@@ -16441,16 +18055,24 @@
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>色降2之血玫瑰</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>色降2之血玫瑰</t>
+        </is>
+      </c>
       <c r="T208" t="n">
         <v>0</v>
       </c>
@@ -16515,24 +18137,30 @@
           <t>https://movie.douban.com/subject/26951654/</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr"/>
+      <c r="O209" t="n">
+        <v>11552.42857142857</v>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>红楼梦</t>
+        </is>
+      </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -16595,16 +18223,24 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>愈穷愈见鬼</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>愈穷愈见鬼</t>
+        </is>
+      </c>
       <c r="T210" t="n">
         <v>0</v>
       </c>
@@ -16672,16 +18308,24 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>贴身情人</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>贴身情人</t>
+        </is>
+      </c>
       <c r="T211" t="n">
         <v>0</v>
       </c>
@@ -16749,16 +18393,24 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>人头肉骨茶面</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>人头肉骨茶面</t>
+        </is>
+      </c>
       <c r="T212" t="n">
         <v>0</v>
       </c>
@@ -16826,16 +18478,24 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr"/>
-      <c r="S213" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>极乐酷刑</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>极乐酷刑</t>
+        </is>
+      </c>
       <c r="T213" t="n">
         <v>0</v>
       </c>
@@ -16899,16 +18559,24 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr"/>
-      <c r="S214" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>空虚少妇性告白</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>空虚少妇性告白</t>
+        </is>
+      </c>
       <c r="T214" t="n">
         <v>0</v>
       </c>
@@ -16976,16 +18644,24 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>阳光地狱之人肉市场</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>阳光地狱之人肉市场</t>
+        </is>
+      </c>
       <c r="T215" t="n">
         <v>0</v>
       </c>
@@ -17053,16 +18729,24 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>玉蒲团之云雨山庄</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>玉蒲团之云雨山庄</t>
+        </is>
+      </c>
       <c r="T216" t="n">
         <v>0</v>
       </c>
@@ -17127,21 +18811,27 @@
           <t>https://movie.douban.com/subject/27016589/</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr"/>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>三十儿立</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>三十儿立</t>
+        </is>
+      </c>
       <c r="T217" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U217" t="n">
         <v>0</v>
@@ -17207,16 +18897,24 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>色欲中环</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>色欲中环</t>
+        </is>
+      </c>
       <c r="T218" t="n">
         <v>0</v>
       </c>
@@ -17284,16 +18982,24 @@
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>聊斋之欲焰三娘子</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>聊斋之欲焰三娘子</t>
+        </is>
+      </c>
       <c r="T219" t="n">
         <v>0</v>
       </c>
@@ -17361,16 +19067,24 @@
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>色降2：万里驱魔</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>色降2</t>
+        </is>
+      </c>
       <c r="T220" t="n">
         <v>0</v>
       </c>
@@ -17438,16 +19152,24 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>极度强奸</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>极度强奸</t>
+        </is>
+      </c>
       <c r="T221" t="n">
         <v>0</v>
       </c>
@@ -17515,16 +19237,24 @@
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>极欲燃烧</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>极欲燃烧</t>
+        </is>
+      </c>
       <c r="T222" t="n">
         <v>0</v>
       </c>
@@ -17592,16 +19322,24 @@
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>夏日狂情</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>夏日狂情</t>
+        </is>
+      </c>
       <c r="T223" t="n">
         <v>0</v>
       </c>
@@ -17669,16 +19407,24 @@
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>黑萝莉与白萝莉</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>黑萝莉与白萝莉</t>
+        </is>
+      </c>
       <c r="T224" t="n">
         <v>0</v>
       </c>
@@ -17746,16 +19492,24 @@
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>一夜情深</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>一夜情深</t>
+        </is>
+      </c>
       <c r="T225" t="n">
         <v>0</v>
       </c>
@@ -17820,24 +19574,30 @@
           <t>https://movie.douban.com/subject/25917896/</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr"/>
+      <c r="O226" t="n">
+        <v>1257</v>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R226" t="inlineStr"/>
-      <c r="S226" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>沙西米</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>沙西米</t>
+        </is>
+      </c>
       <c r="T226" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U226" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227">
@@ -17897,24 +19657,30 @@
           <t>https://movie.douban.com/subject/25769969/</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr"/>
+      <c r="O227" t="n">
+        <v>2262.857142857143</v>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr"/>
-      <c r="S227" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>绿茶妹2</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>绿茶妹2</t>
+        </is>
+      </c>
       <c r="T227" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -17977,16 +19743,24 @@
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>强奸5：广告诱惑</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>强奸5</t>
+        </is>
+      </c>
       <c r="T228" t="n">
         <v>0</v>
       </c>
@@ -18054,16 +19828,24 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R229" t="inlineStr"/>
-      <c r="S229" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>聊斋艳奇之陆判性经</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>聊斋艳奇之陆判性经</t>
+        </is>
+      </c>
       <c r="T229" t="n">
         <v>0</v>
       </c>
@@ -18131,16 +19913,24 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr"/>
-      <c r="S230" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>三奸</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>三奸</t>
+        </is>
+      </c>
       <c r="T230" t="n">
         <v>0</v>
       </c>
@@ -18208,16 +19998,24 @@
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>异空危情</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>异空危情</t>
+        </is>
+      </c>
       <c r="T231" t="n">
         <v>0</v>
       </c>
@@ -18285,16 +20083,24 @@
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>齐天大性之大闹女儿国</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>齐天大性之大闹女儿国</t>
+        </is>
+      </c>
       <c r="T232" t="n">
         <v>0</v>
       </c>
@@ -18362,16 +20168,24 @@
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>聊斋艳奇之月宫宝盒</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>聊斋艳奇之月宫宝盒</t>
+        </is>
+      </c>
       <c r="T233" t="n">
         <v>0</v>
       </c>
@@ -18439,16 +20253,24 @@
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>聊斋画皮</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>聊斋画皮</t>
+        </is>
+      </c>
       <c r="T234" t="n">
         <v>0</v>
       </c>
@@ -18516,16 +20338,24 @@
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>齐天大性之大破盘丝洞</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>齐天大性之大破盘丝洞</t>
+        </is>
+      </c>
       <c r="T235" t="n">
         <v>0</v>
       </c>
@@ -18593,16 +20423,24 @@
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R236" t="inlineStr"/>
-      <c r="S236" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>聊斋婴宁</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>聊斋婴宁</t>
+        </is>
+      </c>
       <c r="T236" t="n">
         <v>0</v>
       </c>
@@ -18670,16 +20508,24 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R237" t="inlineStr"/>
-      <c r="S237" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>聊斋荷花三娘子</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>聊斋荷花三娘子</t>
+        </is>
+      </c>
       <c r="T237" t="n">
         <v>0</v>
       </c>
@@ -18747,16 +20593,24 @@
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R238" t="inlineStr"/>
-      <c r="S238" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>桃色交易之呻吟</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>桃色交易之呻吟</t>
+        </is>
+      </c>
       <c r="T238" t="n">
         <v>0</v>
       </c>
@@ -18821,21 +20675,27 @@
           <t>https://movie.douban.com/subject/25768127/</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr"/>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R239" t="inlineStr"/>
-      <c r="S239" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>合租客</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>合租客</t>
+        </is>
+      </c>
       <c r="T239" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U239" t="n">
         <v>0</v>
@@ -18901,16 +20761,24 @@
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R240" t="inlineStr"/>
-      <c r="S240" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>潜规则</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>潜规则</t>
+        </is>
+      </c>
       <c r="T240" t="n">
         <v>0</v>
       </c>
@@ -18975,24 +20843,30 @@
           <t>https://movie.douban.com/subject/25795316/</t>
         </is>
       </c>
-      <c r="O241" t="inlineStr"/>
+      <c r="O241" t="n">
+        <v>2077.571428571428</v>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr"/>
-      <c r="S241" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>欲</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>欲</t>
+        </is>
+      </c>
       <c r="T241" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U241" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -19055,16 +20929,24 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>负二代</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>负二代</t>
+        </is>
+      </c>
       <c r="T242" t="n">
         <v>0</v>
       </c>
@@ -19132,16 +21014,24 @@
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R243" t="inlineStr"/>
-      <c r="S243" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>嫩模圈</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>嫩模圈</t>
+        </is>
+      </c>
       <c r="T243" t="n">
         <v>0</v>
       </c>
@@ -19209,16 +21099,24 @@
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>三体之灵魂危机</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>三体之灵魂危机</t>
+        </is>
+      </c>
       <c r="T244" t="n">
         <v>0</v>
       </c>
@@ -19283,24 +21181,30 @@
           <t>https://movie.douban.com/subject/6110569/</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr"/>
+      <c r="O245" t="n">
+        <v>3954.285714285714</v>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>夜店诡谈</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>夜店诡谈</t>
+        </is>
+      </c>
       <c r="T245" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U245" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="246">
@@ -19360,24 +21264,30 @@
           <t>https://movie.douban.com/subject/6130488/</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr"/>
+      <c r="O246" t="n">
+        <v>714.5714285714286</v>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr"/>
-      <c r="S246" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>水落石出</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>水落石出</t>
+        </is>
+      </c>
       <c r="T246" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U246" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -19437,24 +21347,30 @@
           <t>https://movie.douban.com/subject/24878091/</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr"/>
+      <c r="O247" t="n">
+        <v>1939</v>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr"/>
-      <c r="S247" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>海天盛宴·韦口</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>海天盛宴</t>
+        </is>
+      </c>
       <c r="T247" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U247" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
